--- a/artfynd/A 59178-2022 artfynd.xlsx
+++ b/artfynd/A 59178-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106105651</v>
+        <v>137172456</v>
       </c>
       <c r="B7" t="n">
-        <v>58114</v>
+        <v>58167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,42 +1277,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fridhem, Sm</t>
+          <t>Hultebo äng, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594163</v>
+        <v>594050</v>
       </c>
       <c r="R7" t="n">
-        <v>6395320</v>
+        <v>6395495</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1339,22 +1336,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-01-22</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-01-22</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,16 +1377,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106105651</t>
+          <t>https://artportalen.se/Sighting/137172456</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132159497</v>
+        <v>106105651</v>
       </c>
       <c r="B8" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,21 +1412,24 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fridhem, Fridhem, Sm</t>
+          <t>Fridhem, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594207</v>
+        <v>594163</v>
       </c>
       <c r="R8" t="n">
-        <v>6395283</v>
+        <v>6395320</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2023-01-22</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2023-01-22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,13 +1497,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132159497</t>
+          <t>https://artportalen.se/Sighting/106105651</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133689188</v>
+        <v>132159497</v>
       </c>
       <c r="B9" t="n">
         <v>58136</v>
@@ -1534,7 +1534,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594256</v>
+        <v>594207</v>
       </c>
       <c r="R9" t="n">
-        <v>6395258</v>
+        <v>6395283</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1573,22 +1573,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,6 +1613,123 @@
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132159497</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133689188</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fridhem, Fridhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>594256</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6395258</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/133689188</t>
         </is>
@@ -1628,6 +1745,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59178-2022 artfynd.xlsx
+++ b/artfynd/A 59178-2022 artfynd.xlsx
@@ -1269,7 +1269,7 @@
         <v>137172456</v>
       </c>
       <c r="B7" t="n">
-        <v>58167</v>
+        <v>58180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 59178-2022 artfynd.xlsx
+++ b/artfynd/A 59178-2022 artfynd.xlsx
@@ -1269,7 +1269,7 @@
         <v>137172456</v>
       </c>
       <c r="B7" t="n">
-        <v>58180</v>
+        <v>58182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 59178-2022 artfynd.xlsx
+++ b/artfynd/A 59178-2022 artfynd.xlsx
@@ -1295,11 +1295,7 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hultebo äng, Sm</t>

--- a/artfynd/A 59178-2022 artfynd.xlsx
+++ b/artfynd/A 59178-2022 artfynd.xlsx
@@ -1269,7 +1269,7 @@
         <v>137172456</v>
       </c>
       <c r="B7" t="n">
-        <v>58182</v>
+        <v>58192</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 59178-2022 artfynd.xlsx
+++ b/artfynd/A 59178-2022 artfynd.xlsx
@@ -1269,7 +1269,7 @@
         <v>137172456</v>
       </c>
       <c r="B7" t="n">
-        <v>58192</v>
+        <v>58193</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 59178-2022 artfynd.xlsx
+++ b/artfynd/A 59178-2022 artfynd.xlsx
@@ -1269,7 +1269,7 @@
         <v>137172456</v>
       </c>
       <c r="B7" t="n">
-        <v>58193</v>
+        <v>58194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 59178-2022 artfynd.xlsx
+++ b/artfynd/A 59178-2022 artfynd.xlsx
@@ -1269,7 +1269,7 @@
         <v>137172456</v>
       </c>
       <c r="B7" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
